--- a/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-dwh-hard.xlsx
+++ b/Trắc nghiệm bài kiểm tra đánh giá đầu vào/da-dwh-hard.xlsx
@@ -460,19 +460,19 @@
         <v>Đây là hai trường phái thiết kế DWH kinh điển. Inmon nhấn mạnh tính nhất quán và toàn vẹn dữ liệu toàn doanh nghiệp (Enterprise Data Warehouse - EDW ở dạng chuẩn hóa 3NF). Kimball nhấn mạnh tính thực tế, triển khai nhanh và dễ truy vấn (Dimensional Modeling kết hợp Conformed Dimensions).</v>
       </c>
       <c r="F2" t="str">
+        <v>Inmon chỉ sử dụng định dạng lưu trữ XML; còn Kimball bắt buộc sử dụng định dạng lưu trữ JSON — định dạng dữ liệu lưu</v>
+      </c>
+      <c r="G2" t="str">
         <v>Inmon hướng tiếp cận từ trên xuống (Top-down): Xây dựng kho dữ liệu tổng thể ở dạng chuẩn hóa 3NF trước, sau đó tạo các Data Marts phục vụ phòng ban; Kimball hướng tiếp cận từ dưới lên (Bottom-up): Xây dựng trực tiếp các Data Marts theo mô hình Dimensional Modeling (Star Schema) trước rồi tích hợp lại — Top-down chuẩn hóa vs Bottom-up Dimensional</v>
       </c>
-      <c r="G2" t="str">
+      <c r="H2" t="str">
+        <v>Inmon khuyên doanh nghiệp nên thuê ngoài vận hành kho dữ liệu; còn Kimball khuyên tự xây dựng đội ngũ nội bộ — phương thức quản trị nhân sự</v>
+      </c>
+      <c r="I2" t="str">
         <v>Inmon thiết kế kho dữ liệu chạy trên máy chủ Windows; còn Kimball thiết kế kho dữ liệu chạy trên máy chủ Linux — hệ điều hành máy chủ</v>
       </c>
-      <c r="H2" t="str">
-        <v>Inmon chỉ sử dụng định dạng lưu trữ XML; còn Kimball bắt buộc sử dụng định dạng lưu trữ JSON — định dạng dữ liệu lưu</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Inmon khuyên doanh nghiệp nên thuê ngoài vận hành kho dữ liệu; còn Kimball khuyên tự xây dựng đội ngũ nội bộ — phương thức quản trị nhân sự</v>
-      </c>
       <c r="J2">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="3">
@@ -524,19 +524,19 @@
         <v>Để bảo vệ tính toàn vẹn tham chiếu trong DWH, việc để khóa ngoại NULL trong Fact Table là một bad practice vì nó phá vỡ câu lệnh INNER JOIN khi phân tích. Giải pháp chuẩn là tạo các bản ghi mặc định (ví dụ: Key -1 với mô tả "Unknown/Unregistered") trong Dimension Table để ánh xạ.</v>
       </c>
       <c r="F4" t="str">
+        <v>Tự động sinh ngẫu nhiên một mã khách hàng mới và chèn thêm một hàng mới vào bảng Customer sau mỗi giao dịch — sinh mã ngẫu nhiên</v>
+      </c>
+      <c r="G4" t="str">
         <v>Tạo một bản ghi mặc định trong bảng Customer có `customer_key = -1` (ví dụ: "Khách hàng vãng lai") và trỏ các giao dịch không xác định về khóa này — bản ghi mặc định xử lý NULL</v>
-      </c>
-      <c r="G4" t="str">
-        <v>Cho phép trường `customer_key` trong Fact Table nhận giá trị NULL đối với các giao dịch đó — cho phép NULL trong Fact</v>
       </c>
       <c r="H4" t="str">
         <v>Từ chối không nạp các giao dịch này vào kho dữ liệu để tránh làm sai lệch cấu trúc dữ liệu — lọc bỏ bản ghi thô</v>
       </c>
       <c r="I4" t="str">
-        <v>Tự động sinh ngẫu nhiên một mã khách hàng mới và chèn thêm một hàng mới vào bảng Customer sau mỗi giao dịch — sinh mã ngẫu nhiên</v>
+        <v>Cho phép trường `customer_key` trong Fact Table nhận giá trị NULL đối với các giao dịch đó — cho phép NULL trong Fact</v>
       </c>
       <c r="J4">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="5">
@@ -556,19 +556,19 @@
         <v>Pipelines có thể bị sập giữa chừng do mất điện, mất kết nối mạng. Một pipeline đạt tính Idempotent cho phép kỹ sư chạy lại (retry) từ đầu hoặc chạy lại cho một khoảng thời gian cụ thể (backfill) mà không lo dữ liệu bị nhân đôi (ví dụ: nhờ cơ chế tự động xóa dữ liệu cũ trước khi nạp mới hoặc sử dụng khóa duy nhất).</v>
       </c>
       <c r="F5" t="str">
+        <v>Là đường ống tự động mã hóa dữ liệu truyền tải bằng thuật toán bảo mật AES-256 — mã hóa bảo mật</v>
+      </c>
+      <c r="G5" t="str">
+        <v>Là đường ống bắt buộc phải hoàn thành việc nạp dữ liệu dưới 5 phút bất kể kích thước dữ liệu — giới hạn thời gian chạy</v>
+      </c>
+      <c r="H5" t="str">
         <v>Là đường ống dữ liệu mà khi chạy lại nhiều lần với cùng một tập dữ liệu đầu vào sẽ luôn cho ra cùng một kết quả duy nhất trong kho dữ liệu, không gây trùng lặp bản ghi — chạy lại an toàn không trùng lặp</v>
       </c>
-      <c r="G5" t="str">
+      <c r="I5" t="str">
         <v>Là đường ống tự động sửa chữa mã nguồn code Python khi phát sinh lỗi cú pháp trong quá trình chạy — tự động sửa code</v>
       </c>
-      <c r="H5" t="str">
-        <v>Là đường ống bắt buộc phải hoàn thành việc nạp dữ liệu dưới 5 phút bất kể kích thước dữ liệu — giới hạn thời gian chạy</v>
-      </c>
-      <c r="I5" t="str">
-        <v>Là đường ống tự động mã hóa dữ liệu truyền tải bằng thuật toán bảo mật AES-256 — mã hóa bảo mật</v>
-      </c>
       <c r="J5">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="6">
@@ -591,10 +591,10 @@
         <v>Thiết kế mối quan hệ tự liên kết (Recursive Relationship / Self-Referencing Key) bằng cách thêm cột `manager_key` trong chính bảng Employee trỏ tới `employee_key` của người quản lý — mối quan hệ tự liên kết</v>
       </c>
       <c r="G6" t="str">
+        <v>Gộp toàn bộ thông tin của nhân viên, quản lý và giám đốc vào chung một cột dưới dạng chuỗi văn bản JSON — lưu trữ chuỗi JSON</v>
+      </c>
+      <c r="H6" t="str">
         <v>Tạo ra 3 bảng dữ liệu riêng biệt: Bảng Nhân viên, Bảng Quản lý, Bảng Giám đốc và liên kết chúng lại — phân tách bảng cứng nhắc</v>
-      </c>
-      <c r="H6" t="str">
-        <v>Gộp toàn bộ thông tin của nhân viên, quản lý và giám đốc vào chung một cột dưới dạng chuỗi văn bản JSON — lưu trữ chuỗi JSON</v>
       </c>
       <c r="I6" t="str">
         <v>Không thiết lập liên kết nào, yêu cầu người dùng tự tra cứu sơ đồ tổ chức trên file PDF bên ngoài — không liên kết hệ thống</v>
@@ -620,19 +620,19 @@
         <v>Bảo vệ PII (Personally Identifiable Information) là bắt buộc. Kỹ thuật De-identification tách biệt thông tin cá nhân và dữ liệu phân tích. Dữ liệu phân tích lâm sàng vẫn đầy đủ nhưng không thể liên kết ngược lại danh tính cụ thể nếu không có quyền giải mã bảng PII.</v>
       </c>
       <c r="F7" t="str">
+        <v>Không nạp bất kỳ thông tin bệnh án nào vào kho dữ liệu, chỉ lưu trữ thông tin hóa đơn viện phí — giới hạn phạm vi phân tích</v>
+      </c>
+      <c r="G7" t="str">
+        <v>Yêu cầu bác sĩ tự viết tắt tên bệnh nhân bằng các ký tự ngẫu nhiên khi nhập liệu vào hệ thống — viết tắt thủ công</v>
+      </c>
+      <c r="H7" t="str">
         <v>Tách biệt thông tin định danh cá nhân (PII - như Tên, Số điện thoại) sang một bảng riêng được mã hóa và giới hạn quyền truy cập tối đa; Fact Table chỉ chứa các mã số ID vô danh và dữ liệu bệnh án lâm sàng phục vụ phân tích chung — tách biệt dữ liệu định danh PII</v>
       </c>
-      <c r="G7" t="str">
+      <c r="I7" t="str">
         <v>Mã hóa toàn bộ kho dữ liệu bằng mật khẩu dùng chung duy nhất và cung cấp mật khẩu này cho tất cả nhân viên bệnh viện — chia sẻ mật khẩu chung</v>
       </c>
-      <c r="H7" t="str">
-        <v>Không nạp bất kỳ thông tin bệnh án nào vào kho dữ liệu, chỉ lưu trữ thông tin hóa đơn viện phí — giới hạn phạm vi phân tích</v>
-      </c>
-      <c r="I7" t="str">
-        <v>Yêu cầu bác sĩ tự viết tắt tên bệnh nhân bằng các ký tự ngẫu nhiên khi nhập liệu vào hệ thống — viết tắt thủ công</v>
-      </c>
       <c r="J7">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="8">
@@ -652,19 +652,19 @@
         <v>Việc tính toán lịch tài chính (Financial Year có thể bắt đầu từ tháng 4, hoặc các ngày lễ dịch chuyển như Tết Âm lịch) bằng code SQL khi chạy báo cáo là cực kỳ phức tạp và chậm. Tạo một bảng Date Dimension vật lý được tính toán trước toàn bộ các cờ thuộc tính (cờ ngày lễ, cờ cuối tuần, cờ năm tài chính) giúp câu lệnh báo cáo chỉ cần JOIN đơn giản và chạy cực nhanh.</v>
       </c>
       <c r="F8" t="str">
+        <v>Yêu cầu lập trình viên tự viết các hàm tính toán ngày tháng phức tạp trực tiếp trong câu lệnh SELECT SQL của mỗi báo cáo — tính toán động trong SQL</v>
+      </c>
+      <c r="G8" t="str">
         <v>Xây dựng một bảng chiều Date Dimension vật lý chứa sẵn hàng chục thuộc tính được tính toán trước (như ngày trong tuần, quý tài chính, tuần tài chính, cờ ngày lễ, cờ mùa vụ) cho khoảng 20 năm — bảng chiều Date vật lý tiền tính toán</v>
       </c>
-      <c r="G8" t="str">
-        <v>Yêu cầu lập trình viên tự viết các hàm tính toán ngày tháng phức tạp trực tiếp trong câu lệnh SELECT SQL của mỗi báo cáo — tính toán động trong SQL</v>
-      </c>
       <c r="H8" t="str">
+        <v>Tạo 365 bảng dữ liệu tương ứng với 365 ngày trong năm để lưu trữ thông tin ngày tháng độc lập — phân tách bảng cực đoan</v>
+      </c>
+      <c r="I8" t="str">
         <v>Sử dụng các hàm mặc định của hệ quản trị cơ sở dữ liệu (như YEAR(), MONTH()) để tính toán thời gian khi chạy báo cáo — sử dụng hàm CSDL</v>
       </c>
-      <c r="I8" t="str">
-        <v>Tạo 365 bảng dữ liệu tương ứng với 365 ngày trong năm để lưu trữ thông tin ngày tháng độc lập — phân tách bảng cực đoan</v>
-      </c>
       <c r="J8">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="9">
@@ -684,19 +684,19 @@
         <v>Data Lineage trực quan hóa bản đồ đi của dữ liệu. Khi một chỉ số trên báo cáo PowerBI bị sai (ví dụ: Tổng doanh thu hiển thị âm), DA nhờ Data Lineage có thể truy ngược lại xem chỉ số này được tính từ bảng nào ở DWH, bảng đó được lấy từ file Staging nào, và file đó trích xuất từ API nguồn nào để khoanh vùng sửa lỗi.</v>
       </c>
       <c r="F9" t="str">
-        <v>Theo dõi nguồn gốc, luồng di chuyển và các phép biến đổi của dữ liệu từ hệ thống nguồn đầu vào đi qua các bảng trung gian cho đến báo cáo cuối cùng — theo dõi vòng đời dữ liệu</v>
+        <v>Quản lý danh sách các nhân viên đã thực hiện truy cập đọc dữ liệu trong ngày — lịch sử truy cập bảo mật</v>
       </c>
       <c r="G9" t="str">
         <v>Tính toán tổng số lượng máy chủ vật lý cần thiết để vận hành kho dữ liệu trong tương lai — ước lượng hạ tầng</v>
       </c>
       <c r="H9" t="str">
-        <v>Quản lý danh sách các nhân viên đã thực hiện truy cập đọc dữ liệu trong ngày — lịch sử truy cập bảo mật</v>
+        <v>Theo dõi nguồn gốc, luồng di chuyển và các phép biến đổi của dữ liệu từ hệ thống nguồn đầu vào đi qua các bảng trung gian cho đến báo cáo cuối cùng — theo dõi vòng đời dữ liệu</v>
       </c>
       <c r="I9" t="str">
         <v>Tự động tối ưu hóa tốc độ của các câu lệnh JOIN phức tạp trong cơ sở dữ liệu — tối ưu hóa câu lệnh</v>
       </c>
       <c r="J9">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
     <row r="10">
@@ -716,19 +716,19 @@
         <v>Khi tích hợp nhiều nguồn (Multi-source Integration), việc lệch mã định danh rất phổ biến. Sử dụng bảng ánh xạ chung (Master Data Management - MDM) kết hợp Surrogate Key giúp đồng nhất thực thể sản phẩm trong kho dữ liệu mà không làm ảnh hưởng đến mã lưu ở các hệ thống nguồn độc lập.</v>
       </c>
       <c r="F10" t="str">
+        <v>Ép kiểu mã sản phẩm của hệ thống B sang dạng chuỗi bằng cách thêm chữ "PROD" phía trước số 100 và lưu trực tiếp vào Fact Table — chuẩn hóa chuỗi cục bộ</v>
+      </c>
+      <c r="G10" t="str">
         <v>Thiết kế bảng ánh xạ sản phẩm chung (Product Master) sử dụng Surrogate Key kiểu số nguyên tự sinh làm khóa chính; ở tầng Transform, thực hiện đối chiếu mã nguồn của cả hai hệ thống về khóa chính chung này — bảng ánh xạ chuẩn hóa khóa chính</v>
       </c>
-      <c r="G10" t="str">
-        <v>Ép kiểu mã sản phẩm của hệ thống B sang dạng chuỗi bằng cách thêm chữ "PROD" phía trước số 100 và lưu trực tiếp vào Fact Table — chuẩn hóa chuỗi cục bộ</v>
-      </c>
       <c r="H10" t="str">
+        <v>Yêu cầu khách hàng của hệ thống B phải tự đổi lại mã sản phẩm sang kiểu chữ trên phần mềm của họ — yêu cầu sửa hệ thống nguồn</v>
+      </c>
+      <c r="I10" t="str">
         <v>Tách Fact Table thành hai bảng độc lập tương ứng với hai hệ thống để tránh việc phải đồng bộ hóa mã sản phẩm — phân tách bảng Fact</v>
       </c>
-      <c r="I10" t="str">
-        <v>Yêu cầu khách hàng của hệ thống B phải tự đổi lại mã sản phẩm sang kiểu chữ trên phần mềm của họ — yêu cầu sửa hệ thống nguồn</v>
-      </c>
       <c r="J10">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="11">
@@ -748,19 +748,19 @@
         <v>Data Mesh là xu hướng kiến trúc hiện đại cho doanh nghiệp cực lớn. Thay vì dồn mọi dữ liệu về một đội Data tập trung gây nghẽn cổ chai (bottleneck), Data Mesh trao quyền và trách nhiệm quản lý, làm sạch và cung cấp dữ liệu cho từng domain nghiệp vụ tự quản lý, còn đội Data trung tâm chỉ cung cấp nền tảng hạ tầng dùng chung (Data Infrastructure as a Platform).</v>
       </c>
       <c r="F11" t="str">
-        <v>Dịch chuyển từ quản trị dữ liệu tập trung sang mô hình phi tập trung, phân chia quyền sở hữu dữ liệu theo miền nghiệp vụ (Domain-driven) và coi dữ liệu như một sản phẩm (Data as a Product) — phi tập trung hóa quản trị dữ liệu</v>
+        <v>Bắt buộc toàn bộ dữ liệu phải được lưu dưới dạng các tệp tin Excel mã hóa bảo mật thay vì lưu trong database — Excel hóa cơ sở dữ liệu</v>
       </c>
       <c r="G11" t="str">
         <v>Dịch chuyển từ lưu trữ dữ liệu trên máy chủ đám mây về lưu trữ trên hệ thống máy chủ vật lý đặt tại văn phòng — địa phương hóa lưu trữ</v>
       </c>
       <c r="H11" t="str">
-        <v>Bắt buộc toàn bộ dữ liệu phải được lưu dưới dạng các tệp tin Excel mã hóa bảo mật thay vì lưu trong database — Excel hóa cơ sở dữ liệu</v>
+        <v>Dịch chuyển từ quản trị dữ liệu tập trung sang mô hình phi tập trung, phân chia quyền sở hữu dữ liệu theo miền nghiệp vụ (Domain-driven) và coi dữ liệu như một sản phẩm (Data as a Product) — phi tập trung hóa quản trị dữ liệu</v>
       </c>
       <c r="I11" t="str">
         <v>Loại bỏ hoàn toàn vai trò của các kỹ sư dữ liệu (Data Engineers) ra khỏi quy trình phát triển dự án — loại bỏ kỹ sư dữ liệu</v>
       </c>
       <c r="J11">
-        <v>1</v>
+        <v>3</v>
       </c>
     </row>
   </sheetData>
